--- a/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t xml:space="preserve">Training Plan - AWS DevOps (Cohort-2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Duration: 40 Hrs. | Total Sessions: 9 (4.5 Hrs. each) | Training Mode: Instructor-led Classroom Training</t>
+    <t xml:space="preserve">Total Duration: 40 Hrs. | Total Sessions: 10 (4 Hrs. each) | Training Mode: Instructor-led Classroom Training</t>
   </si>
   <si>
     <t xml:space="preserve">Schedule</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Day-1</t>
   </si>
   <si>
-    <t xml:space="preserve">9:30 AM to 02:00 PM</t>
+    <t xml:space="preserve">10:00 AM to 2:00 PM</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Foundations &amp; Culture 
@@ -494,6 +494,9 @@
       <t xml:space="preserve">•	Create CloudWatch alarm
 •	Monitor EC2 &amp; container metrics</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Day-10</t>
   </si>
   <si>
     <t xml:space="preserve">End-to-End Project Deployment</t>
@@ -685,7 +688,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -714,6 +717,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81D41A"/>
+        <bgColor rgb="FF969696"/>
       </patternFill>
     </fill>
     <fill>
@@ -830,7 +839,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -854,7 +863,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -862,7 +871,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -944,7 +953,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF81D41A"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -968,14 +977,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="55.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="40.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="2" width="8.66"/>
   </cols>
@@ -1025,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>46097</v>
+        <v>46111</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>9</v>
@@ -1043,7 +1052,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>46098</v>
+        <v>46112</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>9</v>
@@ -1051,7 +1060,7 @@
       <c r="D5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="13"/>
@@ -1061,7 +1070,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>46099</v>
+        <v>46113</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>9</v>
@@ -1069,7 +1078,7 @@
       <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="13"/>
@@ -1079,7 +1088,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>46101</v>
+        <v>46114</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>9</v>
@@ -1087,7 +1096,7 @@
       <c r="D7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="13"/>
@@ -1097,7 +1106,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>46104</v>
+        <v>46115</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>9</v>
@@ -1105,7 +1114,7 @@
       <c r="D8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="13"/>
@@ -1115,7 +1124,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>46105</v>
+        <v>46118</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>9</v>
@@ -1123,7 +1132,7 @@
       <c r="D9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="13"/>
@@ -1133,7 +1142,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>9</v>
@@ -1141,7 +1150,7 @@
       <c r="D10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="13"/>
@@ -1151,7 +1160,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>9</v>
@@ -1159,7 +1168,7 @@
       <c r="D11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>32</v>
       </c>
       <c r="F11" s="13"/>
@@ -1169,7 +1178,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>46108</v>
+        <v>46121</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>9</v>
@@ -1183,19 +1192,22 @@
       <c r="F12" s="8"/>
     </row>
     <row r="13" s="14" customFormat="true" ht="210" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>46122</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="D13" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1232,38 +1244,38 @@
   <sheetData>
     <row r="1" s="19" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="18"/>
     </row>
     <row r="2" s="19" customFormat="true" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" s="22" customFormat="true" ht="14" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="21"/>
     </row>
     <row r="4" s="22" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" s="22" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
@@ -1060,7 +1060,7 @@
       <c r="D5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="12" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="13"/>
@@ -1078,7 +1078,7 @@
       <c r="D6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="13"/>
@@ -1114,7 +1114,7 @@
       <c r="D8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="13"/>
@@ -1132,7 +1132,7 @@
       <c r="D9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F9" s="13"/>

--- a/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
@@ -1096,7 +1096,7 @@
       <c r="D7" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="13"/>
@@ -1150,7 +1150,7 @@
       <c r="D10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="13"/>

--- a/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
@@ -1168,7 +1168,7 @@
       <c r="D11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>32</v>
       </c>
       <c r="F11" s="13"/>

--- a/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
+++ b/Training Plan_AWS DevOps (Cohort-2)_40 Hrs.xlsx
@@ -1173,7 +1173,7 @@
       </c>
       <c r="F11" s="13"/>
     </row>
-    <row r="12" s="14" customFormat="true" ht="150" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" s="14" customFormat="true" ht="106" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>33</v>
       </c>
@@ -1186,7 +1186,7 @@
       <c r="D12" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>35</v>
       </c>
       <c r="F12" s="8"/>
